--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486832_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486832_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3333</v>
+        <v>2.3376</v>
       </c>
       <c r="E2" t="n">
-        <v>4.141</v>
+        <v>3.3688</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8077</v>
+        <v>-1.0312</v>
       </c>
       <c r="G2" t="n">
         <v>1.128</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9197</v>
+        <v>0.924</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6545</v>
+        <v>0.8823</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2652</v>
+        <v>0.0417</v>
       </c>
       <c r="V2" t="n">
         <v>0.2856</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7698</v>
+        <v>1.4887</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5646</v>
+        <v>1.4821</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2052</v>
+        <v>0.0065</v>
       </c>
       <c r="G3" t="n">
         <v>0.8612</v>
@@ -688,13 +688,13 @@
         <v>0.3862</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6809</v>
+        <v>1.3998</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9856</v>
+        <v>0.9031</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6953</v>
+        <v>0.4966</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4128</v>
+        <v>-0.4335</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7054</v>
+        <v>1.8088</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1182</v>
+        <v>-2.2423</v>
       </c>
       <c r="G4" t="n">
         <v>1.2287</v>
@@ -766,13 +766,13 @@
         <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5516</v>
+        <v>0.5309</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2204</v>
+        <v>0.3238</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3313</v>
+        <v>0.2071</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2277</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5027</v>
+        <v>-0.8889</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7257</v>
+        <v>2.0911</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.2284</v>
+        <v>-2.98</v>
       </c>
       <c r="G5" t="n">
         <v>1.2627</v>
@@ -844,13 +844,13 @@
         <v>0.1931</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2207</v>
+        <v>0.393</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3032</v>
+        <v>0.6687</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5239</v>
+        <v>-0.2756</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6138</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MEJIA ECHEVERRY</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.2529</v>
+        <v>-2.1133</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0377</v>
+        <v>-2.6402</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2151</v>
+        <v>0.5269</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.5217</v>
+        <v>-4.2001</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5036</v>
+        <v>-3.2687</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0181</v>
+        <v>-0.9313</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5755</v>
+        <v>-2.7297</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1927</v>
+        <v>-1.8888</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6172</v>
+        <v>-0.8408</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9462</v>
+        <v>-1.4704</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3109</v>
+        <v>-1.3799</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6354</v>
+        <v>-0.0905</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5461</v>
+        <v>-0.0483</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3038</v>
+        <v>0.0202</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2423</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5712</v>
+        <v>1.5559</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5712</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>J. MEJIA ECHEVERRY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4165</v>
+        <v>-2.7895</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.571</v>
+        <v>-1.6241</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1545</v>
+        <v>-1.1655</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.2001</v>
+        <v>-2.5217</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.2687</v>
+        <v>-2.5036</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9313</v>
+        <v>-0.0181</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.7297</v>
+        <v>-0.5755</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8888</v>
+        <v>-1.1927</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8408</v>
+        <v>0.6172</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4704</v>
+        <v>-1.9462</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3799</v>
+        <v>-1.3109</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0905</v>
+        <v>-0.6354</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3516</v>
+        <v>-0.0828</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9106</v>
+        <v>0.1099</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.441</v>
+        <v>-0.1927</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5559</v>
+        <v>-0.5712</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3282</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.1495</v>
+        <v>-4.3826</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5127</v>
+        <v>-2.0438</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6368</v>
+        <v>-2.3388</v>
       </c>
       <c r="G8" t="n">
         <v>-3.348</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3807</v>
+        <v>0.3862</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3859</v>
+        <v>0.8548</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.4686</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>L. BUENO CASTILLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1929</v>
+        <v>-6.1031</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1047</v>
+        <v>-5.262</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.0881</v>
+        <v>-0.8411</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3885</v>
+        <v>-2.5389</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.744</v>
+        <v>-2.254</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3556</v>
+        <v>-0.2848</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0472</v>
+        <v>-0.8416</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0883</v>
+        <v>-0.8054</v>
       </c>
       <c r="L9" t="n">
-        <v>3.1356</v>
+        <v>-0.0361</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4357</v>
+        <v>-1.6973</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6557</v>
+        <v>-1.4486</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.78</v>
+        <v>-0.2487</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3169</v>
+        <v>-2.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.2823</v>
+        <v>-4.0546</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1956</v>
+        <v>0.1309</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1303</v>
+        <v>-0.3658</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0653</v>
+        <v>0.4967</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.6831</v>
+        <v>-1.1851</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.6831</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. BUENO CASTILLO</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.6698</v>
+        <v>-6.3334</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.7791</v>
+        <v>-1.7735</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8907</v>
+        <v>-4.5599</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5389</v>
+        <v>-1.3885</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.254</v>
+        <v>-3.744</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2848</v>
+        <v>2.3556</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8416</v>
+        <v>1.0472</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8054</v>
+        <v>-2.0883</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0361</v>
+        <v>3.1356</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6973</v>
+        <v>-2.4357</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4486</v>
+        <v>-1.6557</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2487</v>
+        <v>-0.78</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.51</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.0546</v>
+        <v>-3.2823</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4359</v>
+        <v>1.055</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8829</v>
+        <v>0.4616</v>
       </c>
       <c r="U10" t="n">
-        <v>0.447</v>
+        <v>0.5934</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1851</v>
+        <v>-3.6831</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1851</v>
+        <v>-3.6831</v>
       </c>
     </row>
     <row r="11">
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-19.494</v>
+        <v>-19.218</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.868499999999999</v>
+        <v>-4.592800000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.6253</v>
+        <v>-14.6254</v>
       </c>
       <c r="G11" t="n">
         <v>-9.5166</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.8939</v>
+        <v>-6.893899999999999</v>
       </c>
       <c r="I11" t="n">
         <v>-2.6225</v>
@@ -1303,22 +1303,22 @@
         <v>-5.833100000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.7231</v>
+        <v>-7.723100000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>-17.3772</v>
       </c>
       <c r="R11" t="n">
-        <v>9.654</v>
+        <v>9.654000000000002</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4128</v>
+        <v>4.6887</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5826</v>
+        <v>3.8586</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8303</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-6.6671</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.515</v>
+        <v>11.2018</v>
       </c>
       <c r="E12" t="n">
-        <v>9.5372</v>
+        <v>9.4338</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9778</v>
+        <v>1.768</v>
       </c>
       <c r="G12" t="n">
         <v>3.7642</v>
@@ -1390,13 +1390,13 @@
         <v>3.0892</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1487</v>
+        <v>-0.4619</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0271</v>
+        <v>-0.0764</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1758</v>
+        <v>-0.3855</v>
       </c>
       <c r="V12" t="n">
         <v>5.1964</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7797</v>
+        <v>4.7301</v>
       </c>
       <c r="E13" t="n">
         <v>4.0138</v>
       </c>
       <c r="F13" t="n">
-        <v>0.766</v>
+        <v>0.7163</v>
       </c>
       <c r="G13" t="n">
         <v>3.5715</v>
@@ -1468,13 +1468,13 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5295</v>
+        <v>-0.5792</v>
       </c>
       <c r="T13" t="n">
         <v>-0.6347</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1051</v>
+        <v>0.0555</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1047</v>
+        <v>2.6221</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0852</v>
+        <v>0.4647</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0195</v>
+        <v>2.1574</v>
       </c>
       <c r="G14" t="n">
         <v>1.9889</v>
@@ -1546,13 +1546,13 @@
         <v>2.8962</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5792</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2132</v>
+        <v>0.5926</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6339</v>
+        <v>-0.496</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0426</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6578</v>
+        <v>1.9173</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2724</v>
+        <v>1.0422</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9302</v>
+        <v>0.8751</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6529</v>
+        <v>1.8732</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7863</v>
+        <v>-0.0349</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1334</v>
+        <v>1.9081</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.2657</v>
+        <v>1.8601</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2341</v>
+        <v>0.1035</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0315</v>
+        <v>1.7566</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3872</v>
+        <v>0.0131</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5522</v>
+        <v>-0.1384</v>
       </c>
       <c r="O15" t="n">
-        <v>0.165</v>
+        <v>0.1514</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.3515</v>
       </c>
       <c r="R15" t="n">
-        <v>2.51</v>
+        <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3031</v>
+        <v>0.3724</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1106</v>
+        <v>0.248</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1925</v>
+        <v>0.1243</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4554</v>
+        <v>-0.3282</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4554</v>
+        <v>0.2856</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2415</v>
+        <v>1.8369</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.1413</v>
       </c>
       <c r="F16" t="n">
-        <v>0.613</v>
+        <v>1.6956</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8732</v>
+        <v>-1.6529</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0349</v>
+        <v>-1.7863</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9081</v>
+        <v>0.1334</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8601</v>
+        <v>-1.2657</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1035</v>
+        <v>-1.2341</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7566</v>
+        <v>-0.0315</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0131</v>
+        <v>-0.3872</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1384</v>
+        <v>-0.5522</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1514</v>
+        <v>0.165</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1585</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.3515</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>2.51</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3034</v>
+        <v>-0.124</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1657</v>
+        <v>0.3031</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1377</v>
+        <v>-0.4271</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3282</v>
+        <v>2.4554</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>2.4554</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1751</v>
+        <v>1.2841</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5635</v>
+        <v>0.4601</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6116</v>
+        <v>0.824</v>
       </c>
       <c r="G17" t="n">
         <v>0.363</v>
@@ -1780,13 +1780,13 @@
         <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2538</v>
+        <v>-0.1448</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6065</v>
+        <v>0.5031</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8603</v>
+        <v>-0.6479</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2856</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2103</v>
+        <v>0.2599</v>
       </c>
       <c r="E18" t="n">
         <v>0.0189</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1914</v>
+        <v>0.2411</v>
       </c>
       <c r="G18" t="n">
         <v>0.7564</v>
@@ -1858,13 +1858,13 @@
         <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.353</v>
+        <v>-0.3034</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2427</v>
+        <v>-0.193</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. TEVAR TEVAR</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0208</v>
+        <v>0.0434</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.5135</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0208</v>
+        <v>-0.47</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4069</v>
+        <v>-0.5321</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4069</v>
+        <v>-1.4762</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.1244</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.6826</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4069</v>
+        <v>-0.6564</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.1371</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4069</v>
+        <v>-0.7935</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3862</v>
+        <v>1.7377</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-1.7101</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.9374</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1271</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>M. TEVAR TEVAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3042</v>
+        <v>-0.0208</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5135</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8177</v>
+        <v>-0.0208</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5321</v>
+        <v>-0.4069</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9441000000000001</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4762</v>
+        <v>-0.4069</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1244</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8070000000000001</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6826</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6564</v>
+        <v>-0.4069</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1371</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7935</v>
+        <v>-0.4069</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0578</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2851</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1271</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.7396</v>
       </c>
       <c r="E21" t="n">
         <v>1.2955</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.184</v>
+        <v>-2.0351</v>
       </c>
       <c r="G21" t="n">
         <v>1.764</v>
@@ -2092,13 +2092,13 @@
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4248</v>
+        <v>-0.2759</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3863</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0386</v>
+        <v>0.1104</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8415</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9766</v>
+        <v>-2.9518</v>
       </c>
       <c r="E22" t="n">
         <v>-2.7582</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2184</v>
+        <v>-0.1936</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9726</v>
@@ -2170,13 +2170,13 @@
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6179</v>
+        <v>-0.593</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4966</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1212</v>
+        <v>-0.0964</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>19.4939</v>
+        <v>20.1834</v>
       </c>
       <c r="E23" t="n">
-        <v>14.6255</v>
+        <v>14.6256</v>
       </c>
       <c r="F23" t="n">
-        <v>4.868599999999999</v>
+        <v>5.558</v>
       </c>
       <c r="G23" t="n">
         <v>9.5167</v>
@@ -2224,7 +2224,7 @@
         <v>14.8018</v>
       </c>
       <c r="K23" t="n">
-        <v>8.968700000000002</v>
+        <v>8.9687</v>
       </c>
       <c r="L23" t="n">
         <v>5.8332</v>
@@ -2239,7 +2239,7 @@
         <v>-3.2105</v>
       </c>
       <c r="P23" t="n">
-        <v>7.723</v>
+        <v>7.723000000000002</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.6539</v>
@@ -2248,13 +2248,13 @@
         <v>17.3769</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.4128</v>
+        <v>-3.7233</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8301999999999998</v>
+        <v>-0.8303</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.5827</v>
+        <v>-2.8931</v>
       </c>
       <c r="V23" t="n">
         <v>6.667199999999999</v>
